--- a/outputs/IMAGENES_POR_ITT/itt_pulmon_oriente/ITT_Pulmon_Oriente_Seguridad_T1_2026.xlsx
+++ b/outputs/IMAGENES_POR_ITT/itt_pulmon_oriente/ITT_Pulmon_Oriente_Seguridad_T1_2026.xlsx
@@ -470,7 +470,7 @@
         <v>257</v>
       </c>
       <c r="D2" t="n">
-        <v>9219</v>
+        <v>434</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,10 +481,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         <v>199</v>
       </c>
       <c r="D3" t="n">
-        <v>8217</v>
+        <v>377</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="4">
@@ -526,7 +526,7 @@
         <v>254</v>
       </c>
       <c r="D4" t="n">
-        <v>7502</v>
+        <v>288</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>64.8</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
         <v>271</v>
       </c>
       <c r="D5" t="n">
-        <v>25956</v>
+        <v>1164</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         <v>257</v>
       </c>
       <c r="D2" t="n">
-        <v>9219</v>
+        <v>434</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>258</v>
       </c>
       <c r="D3" t="n">
-        <v>9369</v>
+        <v>376</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         <v>255</v>
       </c>
       <c r="D4" t="n">
-        <v>9422</v>
+        <v>381</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>243</v>
       </c>
       <c r="D5" t="n">
-        <v>7956</v>
+        <v>261</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         <v>199</v>
       </c>
       <c r="D6" t="n">
-        <v>8217</v>
+        <v>377</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>226</v>
       </c>
       <c r="D7" t="n">
-        <v>7962</v>
+        <v>355</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>265</v>
       </c>
       <c r="D8" t="n">
-        <v>7811</v>
+        <v>349</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>7945</v>
+        <v>328</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>254</v>
       </c>
       <c r="D10" t="n">
-        <v>7502</v>
+        <v>288</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>243</v>
       </c>
       <c r="D11" t="n">
-        <v>7491</v>
+        <v>307</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>253</v>
       </c>
       <c r="D12" t="n">
-        <v>7587</v>
+        <v>291</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>312</v>
       </c>
       <c r="D13" t="n">
-        <v>7364</v>
+        <v>260</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>271</v>
       </c>
       <c r="D14" t="n">
-        <v>25956</v>
+        <v>1164</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
